--- a/AAAGameData/DataTables/Skill/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Skill/SkillTable.xlsx
@@ -122,7 +122,7 @@
     <t>临时需求</t>
   </si>
   <si>
-    <t>在目标地点召唤&lt;val1&gt;个码农加入战斗，码农有寿命限制，会在&lt;val2&gt;秒后自动死亡。</t>
+    <t>在目标地点召唤{0}个码农加入战斗，码农有寿命限制，会在{1}秒后自动死亡。</t>
   </si>
   <si>
     <t>6,35</t>
@@ -146,7 +146,7 @@
     <t>到此一游</t>
   </si>
   <si>
-    <t>在目标点留下一个“打卡点”标记，标记附近&lt;val1&gt;码范围内的我方单位攻击速度提升&lt;val2&gt;，标记持续&lt;val3&gt;秒。</t>
+    <t>在目标点留下一个“打卡点”标记，标记附近{0}码范围内的我方单位攻击速度提升{1}，标记持续{2}秒。</t>
   </si>
   <si>
     <t>400,30,8</t>
@@ -167,7 +167,7 @@
     <t>您的外卖</t>
   </si>
   <si>
-    <t>消耗&lt;val1&gt;资源，为英雄及附近&lt;val2&gt;码内的我方单位回复&lt;val3&gt;点生命。</t>
+    <t>消耗{0}橙髓，为英雄及附近{1}码内的我方单位回复{2}点生命。</t>
   </si>
   <si>
     <t>2,300,40</t>
@@ -188,7 +188,7 @@
     <t>刀舞</t>
   </si>
   <si>
-    <t>&lt;val1&gt;秒内，英雄的攻击速度提升&lt;val2&gt;。</t>
+    <t>{0}秒内，英雄的攻击速度提升{1}。</t>
   </si>
   <si>
     <t>6,80</t>
@@ -206,7 +206,7 @@
     <t>消防演习</t>
   </si>
   <si>
-    <t>在目标地点产生&lt;val1&gt;码范围的浓烟，其中的敌人受到致盲效果，攻击有&lt;val2&gt;%的概率落空。</t>
+    <t>在目标地点产生{0}码范围的浓烟，其中的敌人受到致盲效果，攻击有{1}%的概率落空。</t>
   </si>
   <si>
     <t>250,50</t>
@@ -227,7 +227,7 @@
     <t>缓存清理</t>
   </si>
   <si>
-    <t>丢弃单位牌时，英雄回复&lt;val1&gt;%生命。</t>
+    <t>丢弃单位牌时，英雄回复{0}%生命。</t>
   </si>
   <si>
     <t>SkillType.Passive</t>
@@ -245,7 +245,7 @@
     <t>久坐病</t>
   </si>
   <si>
-    <t>英雄停止主动移动超过&lt;val1&gt;秒后，攻击力增加&lt;val2&gt;%，攻击距离增加&lt;val3&gt;%。</t>
+    <t>英雄停止主动移动超过{0}秒后，攻击力增加{1}%，攻击距离增加{2}%。主动移动时该效果消失。</t>
   </si>
   <si>
     <t>2,20,20</t>
@@ -263,7 +263,7 @@
     <t>凑热闹</t>
   </si>
   <si>
-    <t>附近&lt;val1&gt;码内有不少于&lt;val2&gt;个其他我方单位时，英雄攻击速度提升&lt;val3&gt;。</t>
+    <t>附近{0}码内有不少于{1}个其他我方单位时，英雄攻击速度提升{2}。</t>
   </si>
   <si>
     <t>300,4,40</t>
@@ -281,7 +281,7 @@
     <t>轻装上阵</t>
   </si>
   <si>
-    <t>英雄的移动速度+&lt;val1&gt;%。</t>
+    <t>英雄的移动速度+{0}%。</t>
   </si>
   <si>
     <t>Skill_Name_LightLoad</t>
@@ -296,7 +296,7 @@
     <t>强壮</t>
   </si>
   <si>
-    <t>英雄的生命上限+&lt;val1&gt;%。</t>
+    <t>英雄的生命上限+{0}%。</t>
   </si>
   <si>
     <t>Skill_Name_Mighty</t>
@@ -311,7 +311,7 @@
     <t>紧急疏散</t>
   </si>
   <si>
-    <t>英雄血量低于&lt;val1&gt;%时，在&lt;val2&gt;秒内移动速度提升&lt;val3&gt;%。冷却时间&lt;val4&gt;秒。</t>
+    <t>英雄血量低于{0}%时，在{1}秒内移动速度提升{2}%。冷却时间{3}秒。</t>
   </si>
   <si>
     <t>30,5,80,25</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" ht="84.75" spans="1:13">
+    <row r="6" ht="70.75" spans="1:13">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" ht="56.75" spans="1:13">
+    <row r="7" ht="42.75" spans="1:13">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" ht="28" spans="1:13">
+    <row r="8" ht="28.75" spans="1:13">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" ht="56.75" spans="1:13">
+    <row r="11" ht="70.75" spans="1:13">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" ht="56.75" spans="1:13">
+    <row r="12" ht="42.75" spans="1:13">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" ht="28" spans="1:13">
+    <row r="13" ht="28.75" spans="1:13">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" ht="28" spans="1:13">
+    <row r="14" ht="25" customHeight="1" spans="1:13">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" ht="56.75" spans="1:13">
+    <row r="15" ht="42.75" spans="1:13">
       <c r="A15" s="2"/>
       <c r="B15" s="2">
         <v>11</v>

--- a/AAAGameData/DataTables/Skill/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Skill/SkillTable.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$J$1:$J$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>#</t>
   </si>
@@ -53,10 +53,10 @@
     <t>Lv1UsageCount</t>
   </si>
   <si>
-    <t>Lv2UniqueValues</t>
-  </si>
-  <si>
-    <t>Lv2UsageCount</t>
+    <t>UpgradeIncrementUniqueValues</t>
+  </si>
+  <si>
+    <t>UpgradeIncrementUsageCount</t>
   </si>
   <si>
     <t>Type</t>
@@ -80,6 +80,9 @@
     <t>Fix64[]</t>
   </si>
   <si>
+    <t>Fix64</t>
+  </si>
+  <si>
     <t>enum</t>
   </si>
   <si>
@@ -98,10 +101,13 @@
     <t>1级使用次数</t>
   </si>
   <si>
-    <t>2级数值</t>
-  </si>
-  <si>
-    <t>2级使用次数</t>
+    <t>升级增加数值</t>
+  </si>
+  <si>
+    <t>升级增加使用次数</t>
+  </si>
+  <si>
+    <t>冷却时间</t>
   </si>
   <si>
     <t>技能类型</t>
@@ -116,22 +122,79 @@
     <t>Sprite路径</t>
   </si>
   <si>
+    <t>Skill_JustPassingBy</t>
+  </si>
+  <si>
+    <t>到此一游</t>
+  </si>
+  <si>
+    <t>在目标点留下一个“打卡点”标记，标记附近{0}码范围内的我方单位攻击速度提升{1}，标记持续{2}秒。</t>
+  </si>
+  <si>
+    <t>400,30,8</t>
+  </si>
+  <si>
+    <t>50,10,2</t>
+  </si>
+  <si>
+    <t>SkillType.Active</t>
+  </si>
+  <si>
+    <t>Skill_Name_JustPassingBy</t>
+  </si>
+  <si>
+    <t>Skill_Desc_JustPassingBy</t>
+  </si>
+  <si>
+    <t>Skill_BladeDance</t>
+  </si>
+  <si>
+    <t>刀舞</t>
+  </si>
+  <si>
+    <t>{0}秒内，英雄的攻击速度提升{1}。</t>
+  </si>
+  <si>
+    <t>6,80</t>
+  </si>
+  <si>
+    <t>2,30</t>
+  </si>
+  <si>
+    <t>Skill_Name_BladeDance</t>
+  </si>
+  <si>
+    <t>Skill_Desc_BladeDance</t>
+  </si>
+  <si>
+    <t>Skill_FireDrill</t>
+  </si>
+  <si>
+    <t>消防演习</t>
+  </si>
+  <si>
+    <t>在目标地点产生{0}码范围的浓烟，其中的敌人受到致盲效果，攻击有{1}%的概率落空。浓烟持续{2}秒。</t>
+  </si>
+  <si>
+    <t>250,50,7</t>
+  </si>
+  <si>
+    <t>30,10,1</t>
+  </si>
+  <si>
+    <t>Skill_Name_FireDrill</t>
+  </si>
+  <si>
+    <t>Skill_Desc_FireDrill</t>
+  </si>
+  <si>
     <t>Skill_UrgentRequest</t>
   </si>
   <si>
     <t>临时需求</t>
   </si>
   <si>
-    <t>在目标地点召唤{0}个码农加入战斗，码农有寿命限制，会在{1}秒后自动死亡。</t>
-  </si>
-  <si>
-    <t>6,35</t>
-  </si>
-  <si>
-    <t>8,35</t>
-  </si>
-  <si>
-    <t>SkillType.Active</t>
+    <t>在目标点部署{0}名实习生,它们会在35秒后自动死亡。</t>
   </si>
   <si>
     <t>Skill_Name_UrgentRequest</t>
@@ -140,187 +203,121 @@
     <t>Skill_Desc_UrgentRequest</t>
   </si>
   <si>
-    <t>Skill_JustPassingBy</t>
-  </si>
-  <si>
-    <t>到此一游</t>
-  </si>
-  <si>
-    <t>在目标点留下一个“打卡点”标记，标记附近{0}码范围内的我方单位攻击速度提升{1}，标记持续{2}秒。</t>
-  </si>
-  <si>
-    <t>400,30,8</t>
-  </si>
-  <si>
-    <t>450,50,10</t>
-  </si>
-  <si>
-    <t>Skill_Name_JustPassingBy</t>
-  </si>
-  <si>
-    <t>Skill_Desc_JustPassingBy</t>
-  </si>
-  <si>
-    <t>Skill_SpecialDelivery</t>
-  </si>
-  <si>
-    <t>您的外卖</t>
-  </si>
-  <si>
-    <t>消耗{0}橙髓，为英雄及附近{1}码内的我方单位回复{2}点生命。</t>
-  </si>
-  <si>
-    <t>2,300,40</t>
-  </si>
-  <si>
-    <t>2,350,60</t>
-  </si>
-  <si>
-    <t>Skill_Name_SpecialDelivery</t>
-  </si>
-  <si>
-    <t>Skill_Desc_SpecialDelivery</t>
-  </si>
-  <si>
-    <t>Skill_BladeDance</t>
-  </si>
-  <si>
-    <t>刀舞</t>
-  </si>
-  <si>
-    <t>{0}秒内，英雄的攻击速度提升{1}。</t>
-  </si>
-  <si>
-    <t>6,80</t>
-  </si>
-  <si>
-    <t>Skill_Name_BladeDance</t>
-  </si>
-  <si>
-    <t>Skill_Desc_BladeDance</t>
-  </si>
-  <si>
-    <t>Skill_FireDrill</t>
-  </si>
-  <si>
-    <t>消防演习</t>
-  </si>
-  <si>
-    <t>在目标地点产生{0}码范围的浓烟，其中的敌人受到致盲效果，攻击有{1}%的概率落空。</t>
-  </si>
-  <si>
-    <t>250,50</t>
-  </si>
-  <si>
-    <t>300,70</t>
-  </si>
-  <si>
-    <t>Skill_Name_FireDrill</t>
-  </si>
-  <si>
-    <t>Skill_Desc_FireDrill</t>
-  </si>
-  <si>
-    <t>Skill_CacheClear</t>
-  </si>
-  <si>
-    <t>缓存清理</t>
-  </si>
-  <si>
-    <t>丢弃单位牌时，英雄回复{0}%生命。</t>
+    <t>Skill_LightLoad</t>
+  </si>
+  <si>
+    <t>轻装上阵</t>
+  </si>
+  <si>
+    <t>英雄的移动速度+{0}%。</t>
   </si>
   <si>
     <t>SkillType.Passive</t>
   </si>
   <si>
-    <t>Skill_Name_CacheClear</t>
-  </si>
-  <si>
-    <t>Skill_Desc_CacheClear</t>
-  </si>
-  <si>
-    <t>Skill_SedentaryCurse</t>
-  </si>
-  <si>
-    <t>久坐病</t>
-  </si>
-  <si>
-    <t>英雄停止主动移动超过{0}秒后，攻击力增加{1}%，攻击距离增加{2}%。主动移动时该效果消失。</t>
-  </si>
-  <si>
-    <t>2,20,20</t>
-  </si>
-  <si>
-    <t>Skill_Name_SedentaryCurse</t>
-  </si>
-  <si>
-    <t>Skill_Desc_SedentaryCurse</t>
-  </si>
-  <si>
-    <t>Skill_JoinTheFun</t>
-  </si>
-  <si>
-    <t>凑热闹</t>
-  </si>
-  <si>
-    <t>附近{0}码内有不少于{1}个其他我方单位时，英雄攻击速度提升{2}。</t>
-  </si>
-  <si>
-    <t>300,4,40</t>
-  </si>
-  <si>
-    <t>Skill_Name_JoinTheFun</t>
-  </si>
-  <si>
-    <t>Skill_Desc_JoinTheFun</t>
-  </si>
-  <si>
-    <t>Skill_LightLoad</t>
-  </si>
-  <si>
-    <t>轻装上阵</t>
-  </si>
-  <si>
-    <t>英雄的移动速度+{0}%。</t>
-  </si>
-  <si>
     <t>Skill_Name_LightLoad</t>
   </si>
   <si>
     <t>Skill_Desc_LightLoad</t>
   </si>
   <si>
-    <t>Skill_Mighty</t>
-  </si>
-  <si>
-    <t>强壮</t>
-  </si>
-  <si>
-    <t>英雄的生命上限+{0}%。</t>
-  </si>
-  <si>
-    <t>Skill_Name_Mighty</t>
-  </si>
-  <si>
-    <t>Skill_Desc_Mighty</t>
-  </si>
-  <si>
-    <t>Skill_EmergencyEvac</t>
-  </si>
-  <si>
-    <t>紧急疏散</t>
-  </si>
-  <si>
-    <t>英雄血量低于{0}%时，在{1}秒内移动速度提升{2}%。冷却时间{3}秒。</t>
-  </si>
-  <si>
-    <t>30,5,80,25</t>
-  </si>
-  <si>
-    <t>Skill_Name_EmergencyEvac</t>
-  </si>
-  <si>
-    <t>Skill_Desc_EmergencyEvac</t>
+    <t>Skill_Disarm</t>
+  </si>
+  <si>
+    <t>卸除武装</t>
+  </si>
+  <si>
+    <t>英雄对敌方单位造成伤害时，使其攻击-(0)、护甲-(1)，持续{2}秒。（不叠加）</t>
+  </si>
+  <si>
+    <t>5,2,3</t>
+  </si>
+  <si>
+    <t>1,0.5,1</t>
+  </si>
+  <si>
+    <t>Skill_Name_Disarm</t>
+  </si>
+  <si>
+    <t>Skill_Desc_Disarm</t>
+  </si>
+  <si>
+    <t>Skill_GiantSlayer</t>
+  </si>
+  <si>
+    <t>巨人杀手</t>
+  </si>
+  <si>
+    <t>英雄的普通攻击额外造成敌人当前生命{0}%的伤害。</t>
+  </si>
+  <si>
+    <t>Skill_Name_GiantSlayer</t>
+  </si>
+  <si>
+    <t>Skill_Desc_GiantSlayer</t>
+  </si>
+  <si>
+    <t>Skill_Injection</t>
+  </si>
+  <si>
+    <t>打针</t>
+  </si>
+  <si>
+    <t>立刻对英雄附近{0}范围内的敌方单位施加持续{1}秒的恐惧，使其尝试远离恐惧来源。</t>
+  </si>
+  <si>
+    <t>300,4</t>
+  </si>
+  <si>
+    <t>50,1</t>
+  </si>
+  <si>
+    <t>Skill_Name_Injection</t>
+  </si>
+  <si>
+    <t>Skill_Desc_Injection</t>
+  </si>
+  <si>
+    <t>Skill_Cheer Squad</t>
+  </si>
+  <si>
+    <t>啦啦队</t>
+  </si>
+  <si>
+    <t>每有{0}个我方单位在场，英雄便+{1}攻击、+{2}攻速。</t>
+  </si>
+  <si>
+    <t>3,1,2</t>
+  </si>
+  <si>
+    <t>0,0.5,1</t>
+  </si>
+  <si>
+    <t>Skill_Name_Cheer Squad</t>
+  </si>
+  <si>
+    <t>Skill_Desc_Cheer Squad</t>
+  </si>
+  <si>
+    <t>Skill_NeatAndTidy</t>
+  </si>
+  <si>
+    <t>整整齐齐</t>
+  </si>
+  <si>
+    <t>英雄的普通攻击对目标单位周围{0}范围内生命比例更高的单位造成{1}%伤害。</t>
+  </si>
+  <si>
+    <t>200,30</t>
+  </si>
+  <si>
+    <t>30,15</t>
+  </si>
+  <si>
+    <t>Skill_Name_NeatAndTidy</t>
+  </si>
+  <si>
+    <t>Skill_Desc_NeatAndTidy</t>
   </si>
 </sst>
 </file>
@@ -970,7 +967,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -979,6 +976,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1300,7 +1300,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1312,13 +1312,13 @@
     <col min="7" max="7" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.3333333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.1583333333333" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.875" style="1"/>
+    <col min="10" max="12" width="16.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="23.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1583333333333" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1333,15 +1333,16 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="K1" s="2"/>
       <c r="L1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="M1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" ht="28.75" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1365,20 +1366,21 @@
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1406,7 +1408,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
@@ -1414,232 +1416,247 @@
       <c r="M3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" ht="28.75" spans="1:13">
+      <c r="N3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="28.75" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="56.75" spans="1:13">
+        <v>28</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="70.75" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2">
-        <v>3</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>6</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="70.75" spans="1:13">
+        <v>36</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" ht="28.75" spans="1:14">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2">
         <v>2</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>40</v>
+      <c r="H6" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>8</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="42.75" spans="1:13">
+        <v>43</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" ht="74" customHeight="1" spans="1:14">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>8</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="28.75" spans="1:13">
+        <v>50</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:14">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>50</v>
+      <c r="C8" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8</v>
       </c>
       <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8120</v>
+        <v>2</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
       </c>
       <c r="I8" s="2">
-        <v>4</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="74" customHeight="1" spans="1:13">
+      <c r="M8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" ht="28.75" spans="1:14">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="2">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="F9" s="2">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2">
+        <v>12</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="28.75" spans="1:13">
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" ht="56.75" spans="1:14">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>6</v>
@@ -1653,55 +1670,61 @@
       <c r="E10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="2">
-        <v>20</v>
+      <c r="F10" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="70.75" spans="1:13">
+      <c r="M10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" ht="42.75" spans="1:14">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
       <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="42.75" spans="1:13">
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" ht="56.75" spans="1:14">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
@@ -1718,114 +1741,114 @@
       <c r="F12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="s">
-        <v>66</v>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="28.75" spans="1:13">
+      <c r="M12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" ht="42.75" spans="1:14">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="2">
-        <v>15</v>
+        <v>84</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="25" customHeight="1" spans="1:13">
+        <v>87</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" ht="56.75" spans="1:14">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="2">
-        <v>30</v>
+        <v>91</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:13">
+        <v>94</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="2"/>
-      <c r="B15" s="2">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1839,8 +1862,9 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1854,8 +1878,9 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1869,8 +1894,9 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1884,8 +1910,9 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1899,8 +1926,9 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1914,8 +1942,9 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1929,8 +1958,9 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1944,8 +1974,9 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1959,8 +1990,9 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1974,8 +2006,9 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1989,8 +2022,9 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2004,8 +2038,9 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2019,96 +2054,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
+      <c r="N28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/DataTables/Skill/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Skill/SkillTable.xlsx
@@ -305,7 +305,7 @@
     <t>整整齐齐</t>
   </si>
   <si>
-    <t>英雄的普通攻击对目标单位周围{0}范围内生命比例更高的单位造成{1}%伤害。</t>
+    <t>英雄的普通攻击也会对目标附近{0}范围内生命比例更高的单位造成{1}%伤害。</t>
   </si>
   <si>
     <t>200,30</t>

--- a/AAAGameData/DataTables/Skill/SkillTable.xlsx
+++ b/AAAGameData/DataTables/Skill/SkillTable.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$R$1:$R$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -50,15 +50,39 @@
     <t>Lv1UniqueValues</t>
   </si>
   <si>
+    <t>Lv1CastRange</t>
+  </si>
+  <si>
+    <t>Lv1EffectRadius</t>
+  </si>
+  <si>
+    <t>Lv1Duration</t>
+  </si>
+  <si>
     <t>Lv1UsageCount</t>
   </si>
   <si>
+    <t>Lv1Cooldown</t>
+  </si>
+  <si>
     <t>UpgradeIncrementUniqueValues</t>
   </si>
   <si>
+    <t>UpgradeIncrementCastRange</t>
+  </si>
+  <si>
+    <t>UpgradeIncrementEffectRadius</t>
+  </si>
+  <si>
+    <t>UpgradeIncrementDuration</t>
+  </si>
+  <si>
     <t>UpgradeIncrementUsageCount</t>
   </si>
   <si>
+    <t>UpgradeDecrementCooldown</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -98,16 +122,37 @@
     <t>1级数值</t>
   </si>
   <si>
+    <t>1级施法距离</t>
+  </si>
+  <si>
+    <t>1级作用范围</t>
+  </si>
+  <si>
+    <t>1级持续时间</t>
+  </si>
+  <si>
     <t>1级使用次数</t>
   </si>
   <si>
+    <t>1级冷却时间</t>
+  </si>
+  <si>
     <t>升级增加数值</t>
   </si>
   <si>
+    <t>升级增加施法距离</t>
+  </si>
+  <si>
+    <t>升级增加作用范围</t>
+  </si>
+  <si>
+    <t>升级增加持续时间</t>
+  </si>
+  <si>
     <t>升级增加使用次数</t>
   </si>
   <si>
-    <t>冷却时间</t>
+    <t>升级减少冷却时间</t>
   </si>
   <si>
     <t>技能类型</t>
@@ -128,13 +173,7 @@
     <t>到此一游</t>
   </si>
   <si>
-    <t>在目标点留下一个“打卡点”标记，标记附近{0}码范围内的我方单位攻击速度提升{1}，标记持续{2}秒。</t>
-  </si>
-  <si>
-    <t>400,30,8</t>
-  </si>
-  <si>
-    <t>50,10,2</t>
+    <t>在目标点留下一个“打卡点”标记，标记存在期间，其范围内的我方单位+{0}攻速。</t>
   </si>
   <si>
     <t>SkillType.Active</t>
@@ -152,13 +191,7 @@
     <t>刀舞</t>
   </si>
   <si>
-    <t>{0}秒内，英雄的攻击速度提升{1}。</t>
-  </si>
-  <si>
-    <t>6,80</t>
-  </si>
-  <si>
-    <t>2,30</t>
+    <t>技能期间，英雄+{0}攻速。</t>
   </si>
   <si>
     <t>Skill_Name_BladeDance</t>
@@ -173,13 +206,7 @@
     <t>消防演习</t>
   </si>
   <si>
-    <t>在目标地点产生{0}码范围的浓烟，其中的敌人受到致盲效果，攻击有{1}%的概率落空。浓烟持续{2}秒。</t>
-  </si>
-  <si>
-    <t>250,50,7</t>
-  </si>
-  <si>
-    <t>30,10,1</t>
+    <t>在目标地点产生一阵浓烟，浓烟存在期间，其范围内的敌人受到致盲效果，攻击有{0}%的概率落空。</t>
   </si>
   <si>
     <t>Skill_Name_FireDrill</t>
@@ -194,7 +221,7 @@
     <t>临时需求</t>
   </si>
   <si>
-    <t>在目标点部署{0}名实习生,它们会在35秒后自动死亡。</t>
+    <t>在目标点部署{0}名实习生，实习生有寿命限制。</t>
   </si>
   <si>
     <t>Skill_Name_UrgentRequest</t>
@@ -209,7 +236,7 @@
     <t>轻装上阵</t>
   </si>
   <si>
-    <t>英雄的移动速度+{0}%。</t>
+    <t>英雄+{0}%移速。</t>
   </si>
   <si>
     <t>SkillType.Passive</t>
@@ -227,13 +254,13 @@
     <t>卸除武装</t>
   </si>
   <si>
-    <t>英雄对敌方单位造成伤害时，使其攻击-(0)、护甲-(1)，持续{2}秒。（不叠加）</t>
-  </si>
-  <si>
-    <t>5,2,3</t>
-  </si>
-  <si>
-    <t>1,0.5,1</t>
+    <t>对敌方单位造成伤害时，使其在一段时间内-{0}攻击、-{1}护甲。（不叠加）</t>
+  </si>
+  <si>
+    <t>5,2</t>
+  </si>
+  <si>
+    <t>1,0.5</t>
   </si>
   <si>
     <t>Skill_Name_Disarm</t>
@@ -263,13 +290,7 @@
     <t>打针</t>
   </si>
   <si>
-    <t>立刻对英雄附近{0}范围内的敌方单位施加持续{1}秒的恐惧，使其尝试远离恐惧来源。</t>
-  </si>
-  <si>
-    <t>300,4</t>
-  </si>
-  <si>
-    <t>50,1</t>
+    <t>立刻对英雄附近的敌方单位施加恐惧，使其尝试远离恐惧来源。</t>
   </si>
   <si>
     <t>Skill_Name_Injection</t>
@@ -305,13 +326,7 @@
     <t>整整齐齐</t>
   </si>
   <si>
-    <t>英雄的普通攻击也会对目标附近{0}范围内生命比例更高的单位造成{1}%伤害。</t>
-  </si>
-  <si>
-    <t>200,30</t>
-  </si>
-  <si>
-    <t>30,15</t>
+    <t>英雄的普通攻击也会对目标附近生命比例更高的单位造成{0}%伤害。</t>
   </si>
   <si>
     <t>Skill_Name_NeatAndTidy</t>
@@ -1300,7 +1315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1309,16 +1324,17 @@
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="19.8333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="12" width="16.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.1583333333333" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.875" style="1"/>
+    <col min="7" max="10" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="13" max="16" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="17" max="19" width="16.75" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.1583333333333" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1334,15 +1350,22 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" ht="28.75" spans="1:14">
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" ht="28.75" spans="1:21">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1366,473 +1389,645 @@
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>13</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="28.75" spans="1:14">
+        <v>24</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="28.75" spans="1:21">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" ht="70.75" spans="1:14">
+        <v>37</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="56.75" spans="1:21">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G5" s="2">
+        <v>700</v>
+      </c>
+      <c r="H5" s="2">
+        <v>400</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8</v>
+      </c>
+      <c r="J5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="K5" s="2">
+        <v>6</v>
+      </c>
+      <c r="L5" s="2">
+        <v>10</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2">
+        <v>50</v>
+      </c>
+      <c r="O5" s="2">
+        <v>2</v>
+      </c>
+      <c r="P5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="2">
-        <v>6</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" ht="28.75" spans="1:14">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" ht="28.75" spans="1:21">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="2">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
+        <v>6</v>
+      </c>
+      <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="K6" s="2">
+        <v>8</v>
+      </c>
+      <c r="L6" s="3">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
+        <v>2</v>
+      </c>
+      <c r="P6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="2">
-        <v>8</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" ht="74" customHeight="1" spans="1:14">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" ht="74" customHeight="1" spans="1:21">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="2">
+        <v>50</v>
+      </c>
+      <c r="G7" s="2">
+        <v>700</v>
+      </c>
+      <c r="H7" s="2">
+        <v>250</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>8</v>
+      </c>
+      <c r="L7" s="2">
+        <v>10</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <v>30</v>
+      </c>
+      <c r="O7" s="2">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>8</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" ht="42.75" spans="1:14">
+      <c r="S7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:21">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2">
         <v>8</v>
       </c>
       <c r="G8" s="2">
+        <v>700</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="H8" s="2">
+      <c r="K8" s="2">
+        <v>10</v>
+      </c>
+      <c r="L8" s="2">
         <v>2</v>
       </c>
-      <c r="I8" s="2">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2">
         <v>1</v>
       </c>
-      <c r="J8" s="2">
-        <v>10</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" ht="28.75" spans="1:14">
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="2"/>
+    </row>
+    <row r="9" ht="28.75" spans="1:21">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2">
         <v>16</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2">
-        <v>12</v>
-      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>62</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2">
+        <v>12</v>
+      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-    </row>
-    <row r="10" ht="56.75" spans="1:14">
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U9" s="2"/>
+    </row>
+    <row r="10" ht="56.75" spans="1:21">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2">
+        <v>3</v>
+      </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" ht="42.75" spans="1:14">
+      <c r="S10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" ht="42.75" spans="1:21">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2">
-        <v>4</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
+        <v>4</v>
+      </c>
+      <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-    </row>
-    <row r="12" ht="56.75" spans="1:14">
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" ht="42.75" spans="1:21">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="2">
+        <v>86</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="H12" s="2">
+        <v>300</v>
+      </c>
+      <c r="I12" s="2">
+        <v>4</v>
+      </c>
+      <c r="J12" s="2">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="K12" s="2">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2">
+        <v>50</v>
+      </c>
+      <c r="O12" s="2">
         <v>1</v>
       </c>
-      <c r="J12" s="2">
-        <v>8</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" ht="42.75" spans="1:14">
+      <c r="P12" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" ht="42.75" spans="1:21">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-    </row>
-    <row r="14" ht="56.75" spans="1:14">
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" ht="42.75" spans="1:21">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="F14" s="2">
+        <v>30</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>93</v>
+      <c r="H14" s="2">
+        <v>200</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2">
+        <v>15</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2">
+        <v>30</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U14" s="2"/>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1847,8 +2042,15 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1863,8 +2065,15 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1879,8 +2088,15 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1895,8 +2111,15 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1911,8 +2134,15 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1927,8 +2157,15 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1943,8 +2180,15 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1959,8 +2203,15 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1975,8 +2226,15 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -1991,8 +2249,15 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2007,8 +2272,15 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2023,8 +2295,15 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2039,8 +2318,15 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2055,6 +2341,13 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
